--- a/Packages/cn.etetet.twstilemap/Luban/Config/Base/__tables__.xlsx
+++ b/Packages/cn.etetet.twstilemap/Luban/Config/Base/__tables__.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21600"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="YIUI" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="34">
   <si>
     <t>##var</t>
   </si>
@@ -126,6 +126,9 @@
   </si>
   <si>
     <t>TileItem</t>
+  </si>
+  <si>
+    <t>TileItemGroup</t>
   </si>
 </sst>
 </file>
@@ -1070,8 +1073,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultColWidth="16.5" defaultRowHeight="14.25" outlineLevelRow="4"/>
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultColWidth="16.5" defaultRowHeight="14.25" outlineLevelRow="5"/>
   <cols>
     <col min="1" max="1" width="19.5" customWidth="1"/>
     <col min="2" max="3" width="29.375" customWidth="1"/>
@@ -1200,18 +1203,18 @@
         <v>cn.etetet.yiuilubangen.DemoConfigCategory</v>
       </c>
       <c r="E4" t="str">
-        <f>_xlfn.CONCAT(C4,"Config")</f>
+        <f t="shared" ref="E4:E6" si="0">_xlfn.CONCAT(C4,"Config")</f>
         <v>DemoConfig</v>
       </c>
       <c r="F4" t="b">
         <v>1</v>
       </c>
       <c r="G4" t="str">
-        <f>_xlfn.CONCAT("..\..\..\..\cn.etetet.",B4,"\Luban\Config\Datas\",C4,".xlsx")</f>
+        <f t="shared" ref="G4:G6" si="1">_xlfn.CONCAT("..\..\..\..\cn.etetet.",B4,"\Luban\Config\Datas\",C4,".xlsx")</f>
         <v>..\..\..\..\cn.etetet.yiuilubangen\Luban\Config\Datas\Demo.xlsx</v>
       </c>
       <c r="M4" t="str">
-        <f>_xlfn.CONCAT(C4,"ConfigCategory")</f>
+        <f t="shared" ref="M4:M6" si="2">_xlfn.CONCAT(C4,"ConfigCategory")</f>
         <v>DemoConfigCategory</v>
       </c>
     </row>
@@ -1227,19 +1230,46 @@
         <v>cn.etetet.twstilemap.TileItemConfigCategory</v>
       </c>
       <c r="E5" t="str">
-        <f>_xlfn.CONCAT(C5,"Config")</f>
+        <f t="shared" si="0"/>
         <v>TileItemConfig</v>
       </c>
       <c r="F5" t="b">
         <v>1</v>
       </c>
       <c r="G5" t="str">
-        <f>_xlfn.CONCAT("..\..\..\..\cn.etetet.",B5,"\Luban\Config\Datas\",C5,".xlsx")</f>
+        <f t="shared" si="1"/>
         <v>..\..\..\..\cn.etetet.twstilemap\Luban\Config\Datas\TileItem.xlsx</v>
       </c>
       <c r="M5" t="str">
-        <f>_xlfn.CONCAT(C5,"ConfigCategory")</f>
+        <f t="shared" si="2"/>
         <v>TileItemConfigCategory</v>
+      </c>
+    </row>
+    <row r="6" customFormat="1" spans="2:13">
+      <c r="B6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" t="str">
+        <f>_xlfn.CONCAT("cn.etetet.",B6,".",M6)</f>
+        <v>cn.etetet.twstilemap.TileItemGroupConfigCategory</v>
+      </c>
+      <c r="E6" t="str">
+        <f t="shared" si="0"/>
+        <v>TileItemGroupConfig</v>
+      </c>
+      <c r="F6" t="b">
+        <v>1</v>
+      </c>
+      <c r="G6" t="str">
+        <f t="shared" si="1"/>
+        <v>..\..\..\..\cn.etetet.twstilemap\Luban\Config\Datas\TileItemGroup.xlsx</v>
+      </c>
+      <c r="M6" t="str">
+        <f t="shared" si="2"/>
+        <v>TileItemGroupConfigCategory</v>
       </c>
     </row>
   </sheetData>
